--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133073683</v>
+        <v>136713391</v>
       </c>
       <c r="B2" t="n">
-        <v>58658</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,13 +795,257 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136713391</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133073683</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Valbergsvägens vändplan, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>616820</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7008120</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Multrå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133073683</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136713228</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58121</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205974</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Smalnäbbad nötkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes macrorhynchos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>C.L.Brehm, 1823</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valbergsvägens vändplan, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>616820</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7008120</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Multrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136713228</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136713391</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136713228</v>
       </c>
       <c r="B4" t="n">
-        <v>58121</v>
+        <v>58123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136713391</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136713228</v>
       </c>
       <c r="B4" t="n">
-        <v>58123</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136713391</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136713228</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsvägens vändplan, Ång</t>
@@ -955,11 +951,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsvägens vändplan, Ång</t>

--- a/artfynd/A 25964-2026 artfynd.xlsx
+++ b/artfynd/A 25964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136713391</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136713228</v>
       </c>
       <c r="B4" t="n">
-        <v>58138</v>
+        <v>58148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
